--- a/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B147CA3-10FD-42FD-AFCB-3B7EA58677C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D942EF83-41C5-43A3-AA03-A863789A3E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="200">
   <si>
     <t>怪物ID</t>
   </si>
@@ -584,6 +584,42 @@
   </si>
   <si>
     <t>远程前摇停顿帧</t>
+  </si>
+  <si>
+    <t>目标价值</t>
+  </si>
+  <si>
+    <t>COC target value; empty-&gt;1; &lt;0 fail</t>
+  </si>
+  <si>
+    <t>TargetValue</t>
+  </si>
+  <si>
+    <t>障碍寻路模式</t>
+  </si>
+  <si>
+    <t>COC only: around|as-target|ignore; empty=around; illegal fail</t>
+  </si>
+  <si>
+    <t>ObstaclePathMode</t>
+  </si>
+  <si>
+    <t>狂暴要求值</t>
+  </si>
+  <si>
+    <t>D-102 0=never berserk</t>
+  </si>
+  <si>
+    <t>BerserkNoiseThreshold</t>
+  </si>
+  <si>
+    <t>狂暴后仇恨模式</t>
+  </si>
+  <si>
+    <t>D-102 empty=no switch; PassiveChase/StationaryPassive provoke</t>
+  </si>
+  <si>
+    <t>BerserkAggroMode</t>
   </si>
 </sst>
 </file>
@@ -930,10 +966,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE14"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1027,8 +1063,20 @@
       <c r="AE1" t="s">
         <v>29</v>
       </c>
+      <c r="AF1" t="s">
+        <v>188</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>191</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>197</v>
+      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -1119,8 +1167,20 @@
       <c r="AE2" t="s">
         <v>59</v>
       </c>
+      <c r="AF2" t="s">
+        <v>189</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>195</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>198</v>
+      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -1214,8 +1274,20 @@
       <c r="AE3" t="s">
         <v>89</v>
       </c>
+      <c r="AF3" t="s">
+        <v>190</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>193</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>199</v>
+      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>90</v>
       </c>
@@ -1297,8 +1369,11 @@
       <c r="AD4" t="s">
         <v>108</v>
       </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>109</v>
       </c>
@@ -1377,8 +1452,11 @@
       <c r="AD5" t="s">
         <v>119</v>
       </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>120</v>
       </c>
@@ -1457,8 +1535,11 @@
       <c r="AD6" t="s">
         <v>127</v>
       </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>128</v>
       </c>
@@ -1537,8 +1618,11 @@
       <c r="AD7" t="s">
         <v>135</v>
       </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>136</v>
       </c>
@@ -1617,8 +1701,11 @@
       <c r="AD8" t="s">
         <v>140</v>
       </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>141</v>
       </c>
@@ -1697,8 +1784,11 @@
       <c r="AD9" t="s">
         <v>147</v>
       </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>148</v>
       </c>
@@ -1777,8 +1867,11 @@
       <c r="AD10" t="s">
         <v>155</v>
       </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>156</v>
       </c>
@@ -1857,8 +1950,11 @@
       <c r="AD11" t="s">
         <v>162</v>
       </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>163</v>
       </c>
@@ -1937,8 +2033,11 @@
       <c r="AD12" t="s">
         <v>169</v>
       </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>170</v>
       </c>
@@ -2017,8 +2116,11 @@
       <c r="AD13" t="s">
         <v>177</v>
       </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>178</v>
       </c>
@@ -2096,6 +2198,9 @@
       </c>
       <c r="AD14" t="s">
         <v>177</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
